--- a/docs/files/exports/combined-combined-project-checklist.xlsx
+++ b/docs/files/exports/combined-combined-project-checklist.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Combined Web + App Project Checklist</t>
+          <t>Project Delivery Checklist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4,380 words</t>
+          <t>4,281 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Combined Web + App Project Checklist Full-scope project delivery checklist covering all phases for both website and mobile application projects from discovery to launch. Scope: This document covers both Web / Website Pro...</t>
+          <t>Project Delivery Checklist Full-scope project delivery checklist covering all phases — from client discovery through post-launch — for both Website and Mobile Application engagements. Covers: 🌐 Website / Web App &amp;nbsp;|&amp;...</t>
         </is>
       </c>
     </row>
